--- a/mainWidget/mainWidget/src/database/药液物性材料.xlsx
+++ b/mainWidget/mainWidget/src/database/药液物性材料.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>序号</t>
   </si>
@@ -62,176 +62,6 @@
       </rPr>
       <t>W/(m·K)</t>
     </r>
-  </si>
-  <si>
-    <t>丁羟三组元复合推进剂</t>
-  </si>
-  <si>
-    <r>
-      <t>HTPE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>复合推进剂</t>
-    </r>
-  </si>
-  <si>
-    <t>丁羟四组元复合推进剂</t>
-  </si>
-  <si>
-    <r>
-      <t>HTPE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>高能推进剂</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>NEPE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>高能固体推进剂</t>
-    </r>
-  </si>
-  <si>
-    <t>硝酸酯增塑聚醚</t>
-  </si>
-  <si>
-    <t>复合改性双基推进剂</t>
-  </si>
-  <si>
-    <r>
-      <t>CMDB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>推进剂</t>
-    </r>
-  </si>
-  <si>
-    <t>聚丁二烯复合推进剂</t>
-  </si>
-  <si>
-    <r>
-      <t>PBAA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>推进剂</t>
-    </r>
-  </si>
-  <si>
-    <t>高燃速丁羟推进剂</t>
-  </si>
-  <si>
-    <r>
-      <t>高燃速</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>HTPB</t>
-    </r>
-  </si>
-  <si>
-    <t>低燃速丁羟推进剂</t>
-  </si>
-  <si>
-    <r>
-      <t>低燃速</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>HTPB</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">N15 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>高能推进剂</t>
-    </r>
-  </si>
-  <si>
-    <t>高能复合推进剂</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">H16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>高能推进剂</t>
-    </r>
-  </si>
-  <si>
-    <t>低特征信号复合推进剂</t>
-  </si>
-  <si>
-    <t>隐身型推进剂</t>
   </si>
   <si>
     <r>
@@ -249,51 +79,41 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.26</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.25</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.27</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.28</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>THL</t>
+  </si>
+  <si>
+    <t>HTPE 复合推进剂</t>
+  </si>
+  <si>
+    <t>ROTL-1</t>
+  </si>
+  <si>
+    <t>HTPE 高能推进剂</t>
+  </si>
+  <si>
+    <t>RBOL-1</t>
+  </si>
+  <si>
+    <t>NEPE 硝酸酯增塑聚醚推进剂</t>
+  </si>
+  <si>
+    <t>RBHL-1</t>
+  </si>
+  <si>
+    <t>CMDB 改性双基推进剂</t>
+  </si>
+  <si>
+    <t>RBUOL-1</t>
+  </si>
+  <si>
+    <t>PBAA 聚丙烯酸酯推进剂</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,6 +146,10 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -396,11 +220,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -420,10 +245,12 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1"/>
+    <cellStyle name="常规 3" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -690,7 +517,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -698,7 +525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25.92578125" customWidth="1"/>
@@ -706,12 +533,12 @@
     <col min="4" max="6" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -726,205 +553,150 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3">
+    <row r="2" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1780</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1350</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1820</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1380</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="28.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1850</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1420</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1680</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1280</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1780</v>
-      </c>
-      <c r="E2" s="5">
-        <v>1350</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1820</v>
-      </c>
-      <c r="E3" s="5">
-        <v>1380</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1850</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1420</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1680</v>
-      </c>
-      <c r="E5" s="5">
-        <v>1280</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="5">
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1">
         <v>1750</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="1">
         <v>1320</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1800</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1360</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="5">
-        <v>1760</v>
-      </c>
-      <c r="E8" s="5">
-        <v>1330</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1830</v>
-      </c>
-      <c r="E9" s="5">
-        <v>1400</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1840</v>
-      </c>
-      <c r="E10" s="5">
-        <v>1410</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1790</v>
-      </c>
-      <c r="E11" s="5">
-        <v>1370</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>34</v>
-      </c>
+      <c r="F6" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="3"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="3"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/mainWidget/mainWidget/src/database/药液物性材料.xlsx
+++ b/mainWidget/mainWidget/src/database/药液物性材料.xlsx
@@ -159,7 +159,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -195,54 +195,18 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFDEE0E3"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
@@ -517,7 +481,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -525,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25.92578125" customWidth="1"/>
@@ -572,7 +536,7 @@
       <c r="F2" s="1">
         <v>0.22</v>
       </c>
-      <c r="G2" s="7"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
@@ -593,7 +557,7 @@
       <c r="F3" s="1">
         <v>0.24</v>
       </c>
-      <c r="G3" s="7"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" spans="1:7" ht="28.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
@@ -614,7 +578,7 @@
       <c r="F4" s="1">
         <v>0.26</v>
       </c>
-      <c r="G4" s="7"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
@@ -635,7 +599,7 @@
       <c r="F5" s="1">
         <v>0.19</v>
       </c>
-      <c r="G5" s="7"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
@@ -656,47 +620,7 @@
       <c r="F6" s="1">
         <v>0.21</v>
       </c>
-      <c r="G6" s="7"/>
-    </row>
-    <row r="7" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
+      <c r="G6" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/mainWidget/mainWidget/src/database/药液物性材料.xlsx
+++ b/mainWidget/mainWidget/src/database/药液物性材料.xlsx
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -209,7 +209,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -481,7 +480,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -489,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25.92578125" customWidth="1"/>
@@ -497,7 +496,7 @@
     <col min="4" max="6" width="19.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,7 +516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -536,9 +535,8 @@
       <c r="F2" s="1">
         <v>0.22</v>
       </c>
-      <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -557,9 +555,8 @@
       <c r="F3" s="1">
         <v>0.24</v>
       </c>
-      <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" ht="28.75" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:6" ht="28.75" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -578,9 +575,8 @@
       <c r="F4" s="1">
         <v>0.26</v>
       </c>
-      <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -599,9 +595,8 @@
       <c r="F5" s="1">
         <v>0.19</v>
       </c>
-      <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" ht="16.3" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:6" ht="14.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -620,7 +615,6 @@
       <c r="F6" s="1">
         <v>0.21</v>
       </c>
-      <c r="G6" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
